--- a/AAII_Financials/Quarterly/AVGO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AVGO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="92">
   <si>
     <t>AVGO</t>
   </si>
@@ -656,508 +656,532 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="41" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="14" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="43" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46236</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46145</v>
+      </c>
+      <c r="F7" s="2">
         <v>46054</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45963</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45872</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45781</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45690</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45599</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45508</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45417</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45326</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45228</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45137</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45046</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44955</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44864</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44773</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44682</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44591</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44500</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44409</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44318</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44227</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>44136</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>44045</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43954</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43863</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43772</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43681</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43590</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43499</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43408</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>43317</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>43226</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>43135</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AM7" s="2">
         <v>43037</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AN7" s="2">
         <v>42946</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AO7" s="2">
         <v>42855</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AP7" s="2">
         <v>42764</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AQ7" s="2">
         <v>42673</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>29591000</v>
+      </c>
+      <c r="E8" s="3">
+        <v>22187000</v>
+      </c>
+      <c r="F8" s="3">
         <v>19311000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>18015000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>15952000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>15004000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>14916000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>14054000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>13072000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>12487000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>11961000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>9295000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>8876000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>8733000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>8915000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>8930000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>8464000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>8103000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>7706000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>7407000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>6778000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>6610000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>6655000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>6467000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>5821000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>5742000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>5858000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>5776000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>5515000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>5517000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>5789000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>5444000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>5063000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>5014000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AL8" s="3">
         <v>5327000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AM8" s="3">
         <v>4844000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AN8" s="3">
         <v>4463000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AO8" s="3">
         <v>4190000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AP8" s="3">
         <v>4139000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AQ8" s="3">
         <v>4136000</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>7624000</v>
+      </c>
+      <c r="E9" s="3">
+        <v>5301000</v>
+      </c>
+      <c r="F9" s="3">
         <v>4679000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>4213000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>3704000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>3296000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>3273000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>3399000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>3133000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>3142000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>3114000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>2449000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>2272000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>2177000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>2374000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>3003000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>2782000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>2663000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>2637000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>2769000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>2562000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>2552000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>2676000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>2715000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>2490000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>2546000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>2586000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>2615000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>2479000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>2418000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>2525000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>2508000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AJ9" s="3">
         <v>2442000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AK9" s="3">
         <v>2461000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AL9" s="3">
         <v>2684000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AM9" s="3">
         <v>2458000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AN9" s="3">
         <v>2314000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AO9" s="3">
         <v>2204000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AP9" s="3">
         <v>2132000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AQ9" s="3">
         <v>1949000</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>21967000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>16886000</v>
+      </c>
+      <c r="F10" s="3">
         <v>14632000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>13802000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>12248000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>11708000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>11643000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>10655000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>9939000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>9345000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>8847000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>6846000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>6604000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>6556000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>6541000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>5927000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>5682000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>5440000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>5069000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>4638000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>4216000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>4058000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>3979000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>3752000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>3331000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>3196000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>3272000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>3161000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>3036000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>3099000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>3264000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>2936000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AJ10" s="3">
         <v>2621000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AK10" s="3">
         <v>2553000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AL10" s="3">
         <v>2643000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AM10" s="3">
         <v>2386000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AN10" s="3">
         <v>2149000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AO10" s="3">
         <v>1986000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AP10" s="3">
         <v>2007000</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AQ10" s="3">
         <v>2187000</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1199,127 +1223,135 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>2895000</v>
+      </c>
+      <c r="E12" s="3">
+        <v>2995000</v>
+      </c>
+      <c r="F12" s="3">
         <v>2965000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>2981000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>3050000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>2693000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>2253000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>2234000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>2353000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>2415000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>2308000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>1388000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>1358000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>1312000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>1195000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>1197000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>1255000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>1261000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>1206000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>1200000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>1205000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>1238000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>1211000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>1182000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>1228000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AC12" s="3">
         <v>1269000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AD12" s="3">
         <v>1289000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AE12" s="3">
         <v>1177000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AF12" s="3">
         <v>1235000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AG12" s="3">
         <v>1151000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AH12" s="3">
         <v>1133000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AI12" s="3">
         <v>948000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AJ12" s="3">
         <v>959000</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AK12" s="3">
         <v>936000</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AL12" s="3">
         <v>925000</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AM12" s="3">
         <v>828000</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AN12" s="3">
         <v>827000</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AO12" s="3">
         <v>829000</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AP12" s="3">
         <v>808000</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AQ12" s="3">
         <v>806000</v>
       </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1437,186 +1469,198 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>115000</v>
+      </c>
+      <c r="E14" s="3">
+        <v>81000</v>
+      </c>
+      <c r="F14" s="3">
         <v>116000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>387000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>213000</v>
       </c>
-      <c r="G14" s="3">
-        <v>114000</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
+        <v>204000</v>
+      </c>
+      <c r="J14" s="3">
         <v>186000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>930000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>361000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>345000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>712000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>3000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>213000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>9000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>12000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>16000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>8000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>19000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>19000</v>
-      </c>
-      <c r="U14" s="3">
-        <v>26000</v>
-      </c>
-      <c r="V14" s="3">
-        <v>27000</v>
       </c>
       <c r="W14" s="3">
         <v>26000</v>
       </c>
       <c r="X14" s="3">
+        <v>27000</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>26000</v>
+      </c>
+      <c r="Z14" s="3">
         <v>86000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AA14" s="3">
         <v>40000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AB14" s="3">
         <v>67000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AC14" s="3">
         <v>61000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AD14" s="3">
         <v>65000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AE14" s="3">
         <v>47000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AF14" s="3">
         <v>51000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AG14" s="3">
         <v>86000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AH14" s="3">
         <v>629000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AI14" s="3">
         <v>138000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AJ14" s="3">
         <v>21000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AK14" s="3">
         <v>55000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AL14" s="3">
         <v>145000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AM14" s="3">
         <v>187000</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AN14" s="3">
         <v>33000</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AO14" s="3">
         <v>37000</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AP14" s="3">
         <v>211000</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AQ14" s="3">
         <v>469000</v>
       </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>2006000</v>
+      </c>
+      <c r="E15" s="3">
+        <v>1967000</v>
+      </c>
+      <c r="F15" s="3">
         <v>1969000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>2052000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>2026000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>1989000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>1995000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>2415000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>2337000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>2343000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>2172000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>786000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>789000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>789000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>883000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15" s="3">
         <v>358000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>359000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="U15" s="3">
         <v>398000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="V15" s="3">
         <v>397000</v>
-      </c>
-      <c r="U15" s="3">
-        <v>494000</v>
-      </c>
-      <c r="V15" s="3">
-        <v>494000</v>
       </c>
       <c r="W15" s="3">
         <v>494000</v>
@@ -1625,58 +1669,64 @@
         <v>494000</v>
       </c>
       <c r="Y15" s="3">
-        <v>599000</v>
+        <v>494000</v>
       </c>
       <c r="Z15" s="3">
-        <v>600000</v>
+        <v>494000</v>
       </c>
       <c r="AA15" s="3">
         <v>599000</v>
       </c>
       <c r="AB15" s="3">
+        <v>600000</v>
+      </c>
+      <c r="AC15" s="3">
+        <v>599000</v>
+      </c>
+      <c r="AD15" s="3">
         <v>603000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AE15" s="3">
         <v>474000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AF15" s="3">
         <v>475000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AG15" s="3">
         <v>473000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AH15" s="3">
         <v>476000</v>
-      </c>
-      <c r="AG15" s="3">
-        <v>67000</v>
-      </c>
-      <c r="AH15" s="3">
-        <v>68000</v>
       </c>
       <c r="AI15" s="3">
         <v>67000</v>
       </c>
       <c r="AJ15" s="3">
+        <v>68000</v>
+      </c>
+      <c r="AK15" s="3">
+        <v>67000</v>
+      </c>
+      <c r="AL15" s="3">
         <v>339000</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AM15" s="3">
         <v>441000</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AN15" s="3">
         <v>441000</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AO15" s="3">
         <v>442000</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AP15" s="3">
         <v>440000</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AQ15" s="3">
         <v>356000</v>
       </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1715,246 +1765,260 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>13521000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>11318000</v>
+      </c>
+      <c r="F17" s="3">
         <v>10632000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>10137000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>9852000</v>
       </c>
-      <c r="G17" s="3">
-        <v>9061000</v>
-      </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
+        <v>8971000</v>
+      </c>
+      <c r="J17" s="3">
         <v>8470000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>8510000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>8923000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>9177000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>9166000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>5042000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>4807000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>4716000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>4800000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>4944000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>4727000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>4709000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>4598000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>4826000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>4652000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>4635000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>4818000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>4941000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>4813000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>4976000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>5144000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>4722000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>4650000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>4547000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>5234000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>3898000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>3724000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>3813000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AL17" s="3">
         <v>4384000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AM17" s="3">
         <v>4096000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AN17" s="3">
         <v>3815000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AO17" s="3">
         <v>3716000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AP17" s="3">
         <v>3792000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AQ17" s="3">
         <v>3804000</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>16070000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>10869000</v>
+      </c>
+      <c r="F18" s="3">
         <v>8679000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>7878000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>6100000</v>
       </c>
-      <c r="G18" s="3">
-        <v>5943000</v>
-      </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
+        <v>6033000</v>
+      </c>
+      <c r="J18" s="3">
         <v>6446000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>5544000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>4149000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>3310000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>2795000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>4253000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>4069000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>4017000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>4115000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>3986000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>3737000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>3394000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>3108000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>2581000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>2126000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>1975000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>1837000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>1526000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>1008000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>766000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>714000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>1054000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>865000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>970000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>555000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>1546000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>1339000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>1201000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AL18" s="3">
         <v>943000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AM18" s="3">
         <v>748000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AN18" s="3">
         <v>648000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AO18" s="3">
         <v>474000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AP18" s="3">
         <v>347000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AQ18" s="3">
         <v>332000</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1996,281 +2060,295 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-98000</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-118000</v>
+      </c>
+      <c r="F20" s="3">
         <v>-433000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>208000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-205000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-25000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-103000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>396000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-82000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-87000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-185000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>413000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-124000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-113000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-143000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>40000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>6000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-86000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-14000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>22000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>15000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-23000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>117000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>31000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>49000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>130000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>-4000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>54000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>41000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>63000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>68000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>24000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AJ20" s="3">
         <v>39000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AK20" s="3">
         <v>46000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AL20" s="3">
         <v>35000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AM20" s="3">
         <v>16000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AN20" s="3">
         <v>12000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AO20" s="3">
         <v>3000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AP20" s="3">
         <v>31000</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AQ20" s="3">
         <v>9000</v>
       </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>18174000</v>
+      </c>
+      <c r="E21" s="3">
+        <v>12954000</v>
+      </c>
+      <c r="F21" s="3">
         <v>11081000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>9722000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>8331000</v>
       </c>
-      <c r="G21" s="3">
-        <v>7957000</v>
-      </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
+        <v>8047000</v>
+      </c>
+      <c r="J21" s="3">
         <v>8544000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>7563000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>6568000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>5740000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>5152000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>4626000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>4982000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>4919000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>5141000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>5242000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>4960000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>4572000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>4381000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>4104000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>3644000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>3456000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>3487000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>3285000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>2776000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>2626000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>2438000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>2560000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>2356000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>2480000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>2082000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>2538000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>2343000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AK21" s="3">
         <v>2211000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AL21" s="3">
         <v>2162000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AM21" s="3">
         <v>1983000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AN21" s="3">
         <v>1871000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AO21" s="3">
         <v>1670000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AP21" s="3">
         <v>1492000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AQ21" s="3">
         <v>1041000</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>778000</v>
+      </c>
+      <c r="E22" s="3">
+        <v>776000</v>
+      </c>
+      <c r="F22" s="3">
         <v>801000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>761000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>807000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>769000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>873000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>916000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>1064000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>1047000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>926000</v>
-      </c>
-      <c r="M22" s="3">
-        <v>405000</v>
-      </c>
-      <c r="N22" s="3">
-        <v>406000</v>
       </c>
       <c r="O22" s="3">
         <v>405000</v>
@@ -2279,320 +2357,338 @@
         <v>406000</v>
       </c>
       <c r="Q22" s="3">
-        <v>406000</v>
+        <v>405000</v>
       </c>
       <c r="R22" s="3">
         <v>406000</v>
       </c>
       <c r="S22" s="3">
+        <v>406000</v>
+      </c>
+      <c r="T22" s="3">
+        <v>406000</v>
+      </c>
+      <c r="U22" s="3">
         <v>518000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>407000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>434000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>415000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>466000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>570000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>420000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>464000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>487000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>406000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>361000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AF22" s="3">
         <v>362000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AG22" s="3">
         <v>376000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AH22" s="3">
         <v>345000</v>
-      </c>
-      <c r="AG22" s="3">
-        <v>148000</v>
-      </c>
-      <c r="AH22" s="3">
-        <v>149000</v>
       </c>
       <c r="AI22" s="3">
         <v>148000</v>
       </c>
       <c r="AJ22" s="3">
+        <v>149000</v>
+      </c>
+      <c r="AK22" s="3">
+        <v>148000</v>
+      </c>
+      <c r="AL22" s="3">
         <v>183000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AM22" s="3">
         <v>119000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AN22" s="3">
         <v>112000</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AO22" s="3">
         <v>112000</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AP22" s="3">
         <v>111000</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AQ22" s="3">
         <v>106000</v>
       </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>15275000</v>
+      </c>
+      <c r="E23" s="3">
+        <v>10130000</v>
+      </c>
+      <c r="F23" s="3">
         <v>8195000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>6869000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>5285000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>5085000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>5490000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>3763000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>2806000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>2005000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>1342000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>3967000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>3574000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>3716000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>3840000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>3620000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>3337000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>2790000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>2687000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>2169000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>1726000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>1486000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>1384000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>1137000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>593000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>409000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>304000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>747000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>544000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>657000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>278000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>1422000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>1229000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>1099000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AL23" s="3">
         <v>795000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AM23" s="3">
         <v>645000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AN23" s="3">
         <v>548000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AO23" s="3">
         <v>365000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AP23" s="3">
         <v>267000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AQ23" s="3">
         <v>235000</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>2187000</v>
+      </c>
+      <c r="E24" s="3">
+        <v>820000</v>
+      </c>
+      <c r="F24" s="3">
         <v>846000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>-1649000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>1145000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>120000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>-13000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>-442000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>4238000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>-116000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>68000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>443000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>271000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>235000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>66000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>261000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>263000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>200000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>215000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>180000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>-150000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>-7000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>6000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>-187000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>-96000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>-159000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>-76000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>-100000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>-171000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>-36000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>-203000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>281000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AJ24" s="3">
         <v>32000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AK24" s="3">
         <v>-1143000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AL24" s="3">
         <v>24000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AM24" s="3">
         <v>89000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AN24" s="3">
         <v>39000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AO24" s="3">
         <v>-103000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AP24" s="3">
         <v>10000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AQ24" s="3">
         <v>841000</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2710,246 +2806,264 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>13088000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>9310000</v>
+      </c>
+      <c r="F26" s="3">
         <v>7349000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>8518000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>4140000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>4965000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>5503000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>4205000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-1432000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>2121000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>1274000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>3524000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>3303000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>3481000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>3774000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>3359000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>3074000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>2590000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>2472000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>1989000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>1876000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>1493000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>1378000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>1324000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>689000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>568000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>380000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>847000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>715000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>693000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>481000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>1141000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>1197000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>2242000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AL26" s="3">
         <v>771000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AM26" s="3">
         <v>556000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AN26" s="3">
         <v>509000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AO26" s="3">
         <v>468000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AP26" s="3">
         <v>257000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AQ26" s="3">
         <v>-606000</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>13088000</v>
+      </c>
+      <c r="E27" s="3">
+        <v>9310000</v>
+      </c>
+      <c r="F27" s="3">
         <v>7349000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>8518000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>4140000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>4965000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>5503000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>4324000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-1875000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>2121000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>1325000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>3524000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>3303000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>3481000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>3774000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>3311000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>2999000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>2515000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>2398000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>1914000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>1802000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>1417000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>1304000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>1250000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>615000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>493000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>306000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>818000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>715000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>693000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>481000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>1141000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>1197000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>2227000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AL27" s="3">
         <v>435000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AM27" s="3">
         <v>527000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AN27" s="3">
         <v>483000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AO27" s="3">
         <v>444000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AP27" s="3">
         <v>244000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AQ27" s="3">
         <v>-570000</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -3067,8 +3181,14 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -3088,23 +3208,23 @@
         <v>0</v>
       </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
         <v>119000</v>
       </c>
-      <c r="J29" s="3">
+      <c r="L29" s="3">
         <v>-443000</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
         <v>51000</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
-      </c>
-      <c r="N29" s="3">
-        <v>0</v>
-      </c>
       <c r="O29" s="3">
         <v>0</v>
       </c>
@@ -3114,20 +3234,20 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="S29" s="3" t="s">
-        <v>35</v>
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3">
+        <v>0</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
-      </c>
-      <c r="V29" s="3">
-        <v>0</v>
+      <c r="U29" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="V29" s="3" t="s">
+        <v>35</v>
       </c>
       <c r="W29" s="3">
         <v>0</v>
@@ -3139,55 +3259,61 @@
         <v>0</v>
       </c>
       <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AC29" s="3">
         <v>-5000</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AD29" s="3">
         <v>5000</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD29" s="3">
-        <v>0</v>
-      </c>
       <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="3">
         <v>-2000</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AH29" s="3">
         <v>-10000</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AI29" s="3">
         <v>-26000</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AJ29" s="3">
         <v>-1000</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AK29" s="3">
         <v>1491000</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AL29" s="3">
         <v>5795000</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AM29" s="3">
         <v>5000</v>
       </c>
-      <c r="AL29" s="3">
+      <c r="AN29" s="3">
         <v>-2000</v>
       </c>
-      <c r="AM29" s="3">
+      <c r="AO29" s="3">
         <v>-4000</v>
       </c>
-      <c r="AN29" s="3">
+      <c r="AP29" s="3">
         <v>-5000</v>
       </c>
-      <c r="AO29" s="3">
+      <c r="AQ29" s="3">
         <v>-62000</v>
       </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -3305,8 +3431,14 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -3424,246 +3556,264 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>98000</v>
+      </c>
+      <c r="E32" s="3">
+        <v>118000</v>
+      </c>
+      <c r="F32" s="3">
         <v>433000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-208000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>205000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>25000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>103000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-396000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>82000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>87000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>185000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-413000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>124000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>113000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>143000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-40000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-6000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>86000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>14000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-22000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-15000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>23000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-117000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-31000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-49000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-130000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>4000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-54000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>-41000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>-63000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>-68000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>-24000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AJ32" s="3">
         <v>-39000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AK32" s="3">
         <v>-46000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AL32" s="3">
         <v>-35000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AM32" s="3">
         <v>-16000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AN32" s="3">
         <v>-12000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AO32" s="3">
         <v>-3000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AP32" s="3">
         <v>-31000</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AQ32" s="3">
         <v>-9000</v>
       </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>13088000</v>
+      </c>
+      <c r="E33" s="3">
+        <v>9310000</v>
+      </c>
+      <c r="F33" s="3">
         <v>7349000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>8518000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>4140000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>4965000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>5503000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>4324000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-1875000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>2121000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>1325000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>3524000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>3303000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>3481000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>3774000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>3311000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>2999000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>2515000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>2398000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>1914000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>1802000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>1417000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>1304000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>1250000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>614000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>488000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>311000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>818000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>715000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>691000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>471000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>1115000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>1196000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>3718000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AL33" s="3">
         <v>6230000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AM33" s="3">
         <v>532000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AN33" s="3">
         <v>481000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AO33" s="3">
         <v>440000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AP33" s="3">
         <v>239000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AQ33" s="3">
         <v>-632000</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -3781,251 +3931,269 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>13088000</v>
+      </c>
+      <c r="E35" s="3">
+        <v>9310000</v>
+      </c>
+      <c r="F35" s="3">
         <v>7349000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>8518000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>4140000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>4965000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>5503000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>4324000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-1875000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>2121000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>1325000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>3524000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>3303000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>3481000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>3774000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>3311000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>2999000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>2515000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>2398000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>1914000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>1802000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>1417000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>1304000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>1250000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>614000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>488000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>311000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>818000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>715000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>691000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>471000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>1115000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>1196000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>3718000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AL35" s="3">
         <v>6230000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AM35" s="3">
         <v>532000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AN35" s="3">
         <v>481000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AO35" s="3">
         <v>440000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AP35" s="3">
         <v>239000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AQ35" s="3">
         <v>-632000</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46236</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46145</v>
+      </c>
+      <c r="F38" s="2">
         <v>46054</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45963</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45872</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45781</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45690</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45599</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45508</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45417</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45326</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45228</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45137</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45046</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44955</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44864</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44773</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44682</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44591</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44500</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44409</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44318</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44227</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>44136</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>44045</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43954</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43863</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43772</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43681</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43590</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43499</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43408</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>43317</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>43226</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>43135</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AM38" s="2">
         <v>43037</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AN38" s="2">
         <v>42946</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AO38" s="2">
         <v>42855</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AP38" s="2">
         <v>42764</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AQ38" s="2">
         <v>42673</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -4067,8 +4235,10 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -4110,127 +4280,135 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>23975000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>19628000</v>
+      </c>
+      <c r="F41" s="3">
         <v>14174000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>16178000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>10718000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>9472000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>9307000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>9348000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>9952000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>9809000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>11864000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>14189000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>12055000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>11553000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>12647000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>12416000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>9977000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>9005000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>10219000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>12163000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>11105000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>9518000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>9552000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>7618000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>8857000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>9207000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>6444000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>5055000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>5462000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>5328000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>5093000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>4292000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>4136000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>8187000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AL41" s="3">
         <v>7076000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AM41" s="3">
         <v>11204000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AN41" s="3">
         <v>5249000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AO41" s="3">
         <v>4254000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AP41" s="3">
         <v>3536000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AQ41" s="3">
         <v>3097000</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
@@ -4330,502 +4508,532 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
-      <c r="AJ42" s="3" t="s">
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL42" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="AK42" s="3" t="s">
+      <c r="AM42" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AN42" s="3">
         <v>200000</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AO42" s="3">
         <v>200000</v>
       </c>
-      <c r="AN42" s="3" t="s">
+      <c r="AP42" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="AO42" s="3" t="s">
+      <c r="AQ42" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>20894000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>16748000</v>
+      </c>
+      <c r="F43" s="3">
         <v>13996000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>12150000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>10651000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>8797000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>7677000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>6332000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>6222000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>5500000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>4969000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>3653000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>2914000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>3031000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>3234000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>2958000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>2708000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>3083000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>2539000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>2071000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>2234000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>2425000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>2524000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>2297000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>2684000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>3211000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>3651000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>3259000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>3539000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>3484000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>3677000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>3390000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AJ43" s="3">
         <v>3083000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AK43" s="3">
         <v>2836000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AL43" s="3">
         <v>2459000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AM43" s="3">
         <v>2448000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AN43" s="3">
         <v>2417000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AO43" s="3">
         <v>2073000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AP43" s="3">
         <v>1947000</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AQ43" s="3">
         <v>2181000</v>
       </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>4523000</v>
+      </c>
+      <c r="E44" s="3">
+        <v>4328000</v>
+      </c>
+      <c r="F44" s="3">
         <v>2962000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>2270000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>2180000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>2017000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>1908000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>1760000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>1894000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>1842000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>1920000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>1898000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>1842000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>1886000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>1899000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>1925000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>1838000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>1668000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>1520000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>1297000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>1160000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>1004000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>952000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>1003000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>1081000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>953000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>944000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>874000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>1091000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>1034000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>1074000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AI44" s="3">
         <v>1124000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AJ44" s="3">
         <v>1216000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AK44" s="3">
         <v>1235000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AL44" s="3">
         <v>1291000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AM44" s="3">
         <v>1447000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AN44" s="3">
         <v>1431000</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AO44" s="3">
         <v>1311000</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AP44" s="3">
         <v>1336000</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AQ44" s="3">
         <v>1400000</v>
       </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>818000</v>
+      </c>
+      <c r="E45" s="3">
+        <v>369000</v>
+      </c>
+      <c r="F45" s="3">
         <v>289000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>457000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>656000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>959000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>813000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>764000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>809000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>6409000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>7019000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>364000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>1089000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>725000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>447000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>1205000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>1038000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>1054000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>1063000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>1055000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>1137000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>1298000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>1272000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>977000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>1059000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>851000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>1070000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>729000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>806000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>831000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>760000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>301000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AJ45" s="3">
         <v>260000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AK45" s="3">
         <v>216000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AL45" s="3">
         <v>394000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AM45" s="3">
         <v>724000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AN45" s="3">
         <v>646000</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AO45" s="3">
         <v>630000</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AP45" s="3">
         <v>531000</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AQ45" s="3">
         <v>447000</v>
       </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>52173000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>42213000</v>
+      </c>
+      <c r="F46" s="3">
         <v>32062000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>31573000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>24998000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>22181000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>20990000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>19595000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>19947000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>25302000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>27192000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>20847000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>18333000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>17871000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>18836000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>18504000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>15561000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>14810000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>15341000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>16586000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>15636000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>14245000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>14300000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>11895000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>13681000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>14222000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>12109000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>9917000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>10898000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>10677000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>10604000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>9107000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>8695000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AK46" s="3">
         <v>12474000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AL46" s="3">
         <v>11220000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AM46" s="3">
         <v>15823000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AN46" s="3">
         <v>9943000</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AO46" s="3">
         <v>8468000</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AP46" s="3">
         <v>7350000</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AQ46" s="3">
         <v>7125000</v>
       </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4868,11 +5076,11 @@
       <c r="P47" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
-      </c>
-      <c r="R47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="R47" s="3" t="s">
+        <v>35</v>
       </c>
       <c r="S47" s="3">
         <v>0</v>
@@ -4943,246 +5151,264 @@
       <c r="AO47" s="3">
         <v>0</v>
       </c>
+      <c r="AP47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3144000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>2788000</v>
+      </c>
+      <c r="F48" s="3">
         <v>2599000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>3848000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>2451000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>2462000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>2465000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>3846000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>2602000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>2668000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>2662000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>2617000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>2180000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>2209000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>2201000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>2223000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>2250000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>2262000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>2303000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>2348000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>2370000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>2416000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>2496000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>3098000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>3173000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>3231000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>3236000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>2565000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>2611000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>2654000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>2684000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>2635000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AJ48" s="3">
         <v>2695000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AK48" s="3">
         <v>2720000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AL48" s="3">
         <v>2747000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AM48" s="3">
         <v>2599000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AN48" s="3">
         <v>2909000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AO48" s="3">
         <v>2762000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AP48" s="3">
         <v>2646000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AQ48" s="3">
         <v>2509000</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>124126000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>126134000</v>
+      </c>
+      <c r="F49" s="3">
         <v>128103000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>130074000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>132145000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>134194000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>136454000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>138456000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>140907000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>143280000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>144771000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>47520000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>48273000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>49048000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>49839000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>50725000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>51782000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>52844000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>53694000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>54824000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>56176000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>57525000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>58876000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>60229000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>61804000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>63366000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>64937000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>54268000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>55565000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>56850000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>58140000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AI49" s="3">
         <v>37675000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AJ49" s="3">
         <v>38518000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AK49" s="3">
         <v>39254000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AL49" s="3">
         <v>40070000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AM49" s="3">
         <v>35538000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AN49" s="3">
         <v>36633000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AO49" s="3">
         <v>37722000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AP49" s="3">
         <v>38767000</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AQ49" s="3">
         <v>39800000</v>
       </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5300,8 +5526,14 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5419,127 +5651,139 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>8705000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>8023000</v>
+      </c>
+      <c r="F52" s="3">
         <v>7139000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>5597000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>6027000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>5793000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>5449000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>3748000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>4510000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>3961000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>3245000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>1877000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>2809000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>2539000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>2100000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>1797000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>1733000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>1803000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>1886000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>1812000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>1698000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>1338000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>1300000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>711000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>640000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>729000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>724000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>743000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>693000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>735000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>682000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>707000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AJ52" s="3">
         <v>464000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AK52" s="3">
         <v>488000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AL52" s="3">
         <v>507000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AM52" s="3">
         <v>458000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AN52" s="3">
         <v>457000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AO52" s="3">
         <v>897000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AP52" s="3">
         <v>854000</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AQ52" s="3">
         <v>532000</v>
       </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5657,127 +5901,139 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>188148000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>179158000</v>
+      </c>
+      <c r="F54" s="3">
         <v>169903000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>171092000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>165621000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>164630000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>165358000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>165645000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>167966000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>175211000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>177870000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>72861000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>71595000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>71667000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>72976000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>73249000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>71326000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>71719000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>73224000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>75570000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>75880000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>75524000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>76972000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>75933000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>79298000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>81548000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>81006000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>67493000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>69767000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>70916000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>72110000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>50124000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>50372000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>54936000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AL54" s="3">
         <v>54544000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AM54" s="3">
         <v>54418000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AN54" s="3">
         <v>49942000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AO54" s="3">
         <v>49849000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AP54" s="3">
         <v>49617000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AQ54" s="3">
         <v>49966000</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5819,8 +6075,10 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5862,127 +6120,135 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4000000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>2337000</v>
+      </c>
+      <c r="F57" s="3">
         <v>2112000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>1560000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>1432000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>1297000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>1905000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>1662000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>1757000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>1441000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>1496000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>1210000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>992000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>831000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>923000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>998000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>712000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>1069000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>1078000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>1086000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>968000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>830000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>898000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>836000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>1092000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>1230000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>985000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>855000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>996000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>759000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>738000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>811000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AJ57" s="3">
         <v>785000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AK57" s="3">
         <v>836000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AL57" s="3">
         <v>816000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AM57" s="3">
         <v>1105000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AN57" s="3">
         <v>1158000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AO57" s="3">
         <v>925000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AP57" s="3">
         <v>1047000</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AQ57" s="3">
         <v>1261000</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5990,97 +6256,97 @@
         <v>2252000</v>
       </c>
       <c r="E58" s="3">
+        <v>2252000</v>
+      </c>
+      <c r="F58" s="3">
+        <v>2252000</v>
+      </c>
+      <c r="G58" s="3">
         <v>3296000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>1399000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>5531000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>5653000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>1478000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>3161000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>2426000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>2433000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>1668000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>1119000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>1237000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>1229000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>440000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>304000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>302000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>300000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>290000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>279000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>278000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>864000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>827000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>822000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>819000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>2311000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>2787000</v>
-      </c>
-      <c r="AD58" s="3">
-        <v>3537000</v>
-      </c>
-      <c r="AE58" s="3">
-        <v>3537000</v>
       </c>
       <c r="AF58" s="3">
         <v>3537000</v>
       </c>
       <c r="AG58" s="3">
-        <v>0</v>
+        <v>3537000</v>
       </c>
       <c r="AH58" s="3">
-        <v>117000</v>
+        <v>3537000</v>
       </c>
       <c r="AI58" s="3">
-        <v>117000</v>
+        <v>0</v>
       </c>
       <c r="AJ58" s="3">
         <v>117000</v>
@@ -6089,495 +6355,525 @@
         <v>117000</v>
       </c>
       <c r="AL58" s="3">
-        <v>0</v>
+        <v>117000</v>
       </c>
       <c r="AM58" s="3">
-        <v>0</v>
+        <v>117000</v>
       </c>
       <c r="AN58" s="3">
         <v>0</v>
       </c>
       <c r="AO58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ58" s="3">
         <v>454000</v>
       </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>12458000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>12483000</v>
+      </c>
+      <c r="F59" s="3">
         <v>10958000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>10909000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>11510000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>11941000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>11855000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>11051000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>12078000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>14469000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>14822000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>3212000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>3997000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>4427000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>4389000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>5614000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>5686000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>5539000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>4909000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>4905000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>5254000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>5328000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>4932000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>4708000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>4788000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>4552000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>4443000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>3257000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>3749000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>4207000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>4074000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>1527000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AJ59" s="3">
         <v>1285000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AK59" s="3">
         <v>1171000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AL59" s="3">
         <v>1037000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AM59" s="3">
         <v>1307000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AN59" s="3">
         <v>1060000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AO59" s="3">
         <v>1127000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AP59" s="3">
         <v>1075000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AQ59" s="3">
         <v>1363000</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>20838000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>18862000</v>
+      </c>
+      <c r="F60" s="3">
         <v>16859000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>18514000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>16704000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>20597000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>20910000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>16697000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>19221000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>20171000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>20369000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>7405000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>7345000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>7511000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>7483000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>7052000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>6702000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>6910000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>6287000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>6281000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>6501000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>6436000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>6694000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>6371000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>6702000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>6601000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>7739000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>6899000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>8282000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>8503000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>8349000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>2338000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AJ60" s="3">
         <v>2187000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AK60" s="3">
         <v>2124000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AL60" s="3">
         <v>1970000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AM60" s="3">
         <v>2529000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AN60" s="3">
         <v>2218000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AO60" s="3">
         <v>2052000</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AP60" s="3">
         <v>2122000</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AQ60" s="3">
         <v>3078000</v>
       </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>57167000</v>
+      </c>
+      <c r="E61" s="3">
+        <v>62655000</v>
+      </c>
+      <c r="F61" s="3">
         <v>63805000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>63165000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>62830000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>61751000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>60926000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>67438000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>66798000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>71590000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>73468000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>37980000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>38222000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>38194000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>38167000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>39075000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>39218000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>39191000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>39231000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>39467000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>40205000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>40187000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>41094000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>40262000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>43229000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>45072000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>42435000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>30040000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>34028000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>34011000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>34104000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AI61" s="3">
         <v>17493000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AJ61" s="3">
         <v>17487000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AK61" s="3">
         <v>17481000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AL61" s="3">
         <v>17475000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AM61" s="3">
         <v>17431000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AN61" s="3">
         <v>13572000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AO61" s="3">
         <v>13567000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AP61" s="3">
         <v>13562000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AQ61" s="3">
         <v>13188000</v>
       </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>5298000</v>
+      </c>
+      <c r="E62" s="3">
+        <v>4131000</v>
+      </c>
+      <c r="F62" s="3">
         <v>3478000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>1870000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>5227000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>5177000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>5088000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>4029000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>4943000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>5087000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>5131000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>3090000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>3949000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>3955000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>4016000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>4413000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>4530000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>4655000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>4738000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>4860000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>4834000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>4962000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>5211000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>5426000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>5810000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>5933000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>6464000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>5613000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>5954000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>6230000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>6433000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>3636000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AJ62" s="3">
         <v>3246000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AK62" s="3">
         <v>3264000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AL62" s="3">
         <v>6018000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AM62" s="3">
         <v>11272000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AN62" s="3">
         <v>11448000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AO62" s="3">
         <v>11887000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AP62" s="3">
         <v>11923000</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AQ62" s="3">
         <v>11824000</v>
       </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6695,8 +6991,14 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6814,8 +7116,14 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6933,127 +7241,139 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>88458000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>91467000</v>
+      </c>
+      <c r="F66" s="3">
         <v>90031000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>89800000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>92344000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>95044000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>95569000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>97967000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>102315000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>105250000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>107586000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>48873000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>49516000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>49660000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>49666000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>50540000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>50450000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>50756000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>50256000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>50608000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>51540000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>51585000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>52999000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>52059000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>55741000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>57606000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>56638000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>42552000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>48264000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>48744000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>48886000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>23467000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>22920000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AK66" s="3">
         <v>22869000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AL66" s="3">
         <v>28643000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AM66" s="3">
         <v>34133000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AN66" s="3">
         <v>30140000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AO66" s="3">
         <v>30424000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AP66" s="3">
         <v>30584000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AQ66" s="3">
         <v>31074000</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7095,8 +7415,10 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7214,8 +7536,14 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7333,8 +7661,14 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7452,8 +7786,14 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7571,74 +7911,80 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>22151000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>12166000</v>
+      </c>
+      <c r="F72" s="3">
         <v>6520000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>9761000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>4040000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>2686000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>2729000</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="J72" s="3">
-        <v>-1875000</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="L72" s="3" t="s">
+      <c r="L72" s="3">
+        <v>-1875000</v>
+      </c>
+      <c r="M72" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O72" s="3">
         <v>2682000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>1178000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>1363000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>2371000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>1604000</v>
       </c>
-      <c r="R72" s="3">
-        <v>0</v>
-      </c>
-      <c r="S72" s="3">
-        <v>0</v>
-      </c>
       <c r="T72" s="3">
         <v>0</v>
       </c>
       <c r="U72" s="3">
+        <v>0</v>
+      </c>
+      <c r="V72" s="3">
+        <v>0</v>
+      </c>
+      <c r="W72" s="3">
         <v>748000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>320000</v>
       </c>
-      <c r="W72" s="3">
-        <v>0</v>
-      </c>
-      <c r="X72" s="3">
-        <v>0</v>
-      </c>
       <c r="Y72" s="3">
         <v>0</v>
       </c>
@@ -7661,37 +8007,43 @@
         <v>0</v>
       </c>
       <c r="AF72" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG72" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH72" s="3">
         <v>259000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>3487000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>4267000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AK72" s="3">
         <v>7868000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AL72" s="3">
         <v>5132000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AM72" s="3">
         <v>-129000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AN72" s="3">
         <v>-245000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AO72" s="3">
         <v>-311000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AP72" s="3">
         <v>-337000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AQ72" s="3">
         <v>-215000</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7809,8 +8161,14 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7928,8 +8286,14 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8047,127 +8411,139 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>99690000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>87691000</v>
+      </c>
+      <c r="F76" s="3">
         <v>79872000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>81292000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>73277000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>69586000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>69789000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>67678000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>65651000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>69961000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>70284000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>23988000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>22079000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>22007000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>23310000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>22709000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>20876000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>20963000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>22968000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>24962000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>24340000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>23939000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>23973000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>23874000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>23557000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>23942000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>24368000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>24941000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>21503000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>22172000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>23224000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>26657000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>27452000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>32067000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AL76" s="3">
         <v>25901000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AM76" s="3">
         <v>20285000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AN76" s="3">
         <v>19802000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AO76" s="3">
         <v>19425000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AP76" s="3">
         <v>19033000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AQ76" s="3">
         <v>18892000</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8285,251 +8661,269 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46236</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46145</v>
+      </c>
+      <c r="F80" s="2">
         <v>46054</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45963</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45872</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45781</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45690</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45599</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45508</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45417</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45326</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45228</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45137</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45046</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44955</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44864</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44773</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44682</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44591</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44500</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44409</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44318</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44227</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>44136</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>44045</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43954</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43863</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43772</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43681</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43590</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43499</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43408</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>43317</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>43226</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>43135</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AM80" s="2">
         <v>43037</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AN80" s="2">
         <v>42946</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AO80" s="2">
         <v>42855</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AP80" s="2">
         <v>42764</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AQ80" s="2">
         <v>42673</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>13088000</v>
+      </c>
+      <c r="E81" s="3">
+        <v>9310000</v>
+      </c>
+      <c r="F81" s="3">
         <v>7349000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>8518000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>4140000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>4965000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>5503000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>4324000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-1875000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>2121000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>1325000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>3524000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>3303000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>3481000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>3774000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>3311000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>2999000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>2515000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>2398000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>1914000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>1802000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>1417000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>1304000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>1250000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>614000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>488000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>311000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>818000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>715000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>691000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>471000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>1115000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>1196000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>3718000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AL81" s="3">
         <v>6230000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AM81" s="3">
         <v>532000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AN81" s="3">
         <v>481000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AO81" s="3">
         <v>440000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AP81" s="3">
         <v>239000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AQ81" s="3">
         <v>-632000</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8571,127 +8965,135 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>179000</v>
+        <v>142000</v>
       </c>
       <c r="E83" s="3">
-        <v>196000</v>
+        <v>142000</v>
       </c>
       <c r="F83" s="3">
-        <v>187000</v>
+        <v>142000</v>
       </c>
       <c r="G83" s="3">
-        <v>187000</v>
+        <v>156000</v>
       </c>
       <c r="H83" s="3">
-        <v>173000</v>
+        <v>149000</v>
       </c>
       <c r="I83" s="3">
+        <v>149000</v>
+      </c>
+      <c r="J83" s="3">
+        <v>139000</v>
+      </c>
+      <c r="K83" s="3">
         <v>146000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>143000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>150000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>149000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>153000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>153000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>159000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>160000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>1216000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>1217000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>1264000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>1287000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>1501000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>1503000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>1504000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>1533000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>1728000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>1719000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>1730000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>1728000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>1452000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>1450000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>1447000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>1459000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AI83" s="3">
         <v>968000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AJ83" s="3">
         <v>965000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AK83" s="3">
         <v>964000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AL83" s="3">
         <v>1184000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AM83" s="3">
         <v>1219000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AN83" s="3">
         <v>1211000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AO83" s="3">
         <v>1193000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AP83" s="3">
         <v>1114000</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AQ83" s="3">
         <v>700000</v>
       </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8809,8 +9211,14 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8928,8 +9336,14 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9047,8 +9461,14 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9166,8 +9586,14 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9285,127 +9711,139 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>14197000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>10493000</v>
+      </c>
+      <c r="F89" s="3">
         <v>8260000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>7703000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>7166000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>6555000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>6113000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>5604000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>4963000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>4580000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>4815000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>4828000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>4719000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>4502000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>4036000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>4583000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>4424000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>4243000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>3486000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>3541000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>3541000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>3569000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>3113000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>3348000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>3178000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>3213000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>2322000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>2479000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>2419000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>2667000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>2132000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>2635000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>2247000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>2313000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AL89" s="3">
         <v>1685000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AM89" s="3">
         <v>1959000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AN89" s="3">
         <v>1656000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AO89" s="3">
         <v>1583000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AP89" s="3">
         <v>1353000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AQ89" s="3">
         <v>1352000</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9447,127 +9885,135 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-532000</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-231000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-250000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-237000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-142000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-144000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-100000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-122000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-172000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-132000</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-122000</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-105000</v>
       </c>
       <c r="N91" s="3">
         <v>-122000</v>
       </c>
       <c r="O91" s="3">
+        <v>-105000</v>
+      </c>
+      <c r="P91" s="3">
         <v>-122000</v>
-      </c>
-      <c r="P91" s="3">
-        <v>-103000</v>
       </c>
       <c r="Q91" s="3">
         <v>-122000</v>
       </c>
       <c r="R91" s="3">
+        <v>-103000</v>
+      </c>
+      <c r="S91" s="3">
+        <v>-122000</v>
+      </c>
+      <c r="T91" s="3">
         <v>-116000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-85000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-101000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-88000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-115000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-126000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-114000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-102000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-105000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-148000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-108000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-96000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-112000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-125000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-99000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AI91" s="3">
         <v>-106000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AJ91" s="3">
         <v>-120000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AK91" s="3">
         <v>-189000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AL91" s="3">
         <v>-220000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AM91" s="3">
         <v>-233000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AN91" s="3">
         <v>-255000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AO91" s="3">
         <v>-256000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AP91" s="3">
         <v>-325000</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AQ91" s="3">
         <v>-193000</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9685,8 +10131,14 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9804,127 +10256,139 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1113000</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-208000</v>
+      </c>
+      <c r="F94" s="3">
         <v>-115000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-367000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>94000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-133000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-174000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-132000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>3245000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-706000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-25477000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-124000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-144000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-318000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-103000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-128000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>80000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-310000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-309000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>50000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-47000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-126000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-122000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-100000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-46000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>24000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-10987000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-88000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-35000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-106000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-15193000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>-118000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AJ94" s="3">
         <v>-174000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AK94" s="3">
         <v>-155000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AL94" s="3">
         <v>-4227000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AM94" s="3">
         <v>396000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AN94" s="3">
         <v>-258000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AO94" s="3">
         <v>-493000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AP94" s="3">
         <v>-319000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AQ94" s="3">
         <v>26000</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9966,127 +10430,135 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>3103000</v>
+      </c>
+      <c r="E96" s="3">
+        <v>3092000</v>
+      </c>
+      <c r="F96" s="3">
         <v>3086000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>2797000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>2786000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>2785000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>2774000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>2484000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>2452000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>2443000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>2435000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>1904000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>1901000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>1914000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>1926000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>-1782000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="T96" s="3">
         <v>-1736000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="U96" s="3">
         <v>-1750000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="V96" s="3">
         <v>-1764000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="W96" s="3">
         <v>-1561000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="X96" s="3">
         <v>-1556000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="Y96" s="3">
         <v>-1552000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Z96" s="3">
         <v>-1543000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="AA96" s="3">
         <v>-1395000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AB96" s="3">
         <v>-1386000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AC96" s="3">
         <v>-1381000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AD96" s="3">
         <v>-1372000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AE96" s="3">
         <v>-1054000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AF96" s="3">
         <v>-1057000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AG96" s="3">
         <v>-1057000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AH96" s="3">
         <v>-1067000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AI96" s="3">
         <v>-723000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AJ96" s="3">
         <v>-754000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AK96" s="3">
         <v>-766000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AL96" s="3">
         <v>-755000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AM96" s="3">
         <v>-439000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AN96" s="3">
         <v>-438000</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AO96" s="3">
         <v>-437000</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AP96" s="3">
         <v>-431000</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AQ96" s="3">
         <v>-213000</v>
       </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10204,8 +10676,14 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10323,8 +10801,14 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10442,127 +10926,139 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-8737000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-4831000</v>
+      </c>
+      <c r="F100" s="3">
         <v>-10149000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-1876000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-6014000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-6257000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-5980000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-6076000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-8065000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-5929000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>18337000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-2570000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-4073000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-5278000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-3702000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-2016000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-3532000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-5147000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-5121000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-2533000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-1907000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-3477000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-1057000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-4487000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-3482000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-474000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>10054000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-2798000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-2250000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-2326000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>13862000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>-2361000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AJ100" s="3">
         <v>-6124000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AK100" s="3">
         <v>-1047000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AL100" s="3">
         <v>-1586000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AM100" s="3">
         <v>3600000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AN100" s="3">
         <v>-403000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AO100" s="3">
         <v>-372000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AP100" s="3">
         <v>-595000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AQ100" s="3">
         <v>-242000</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10605,11 +11101,11 @@
       <c r="P101" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
-      <c r="R101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="R101" s="3" t="s">
+        <v>35</v>
       </c>
       <c r="S101" s="3">
         <v>0</v>
@@ -10680,123 +11176,135 @@
       <c r="AO101" s="3">
         <v>0</v>
       </c>
+      <c r="AP101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>4347000</v>
+      </c>
+      <c r="E102" s="3">
+        <v>5454000</v>
+      </c>
+      <c r="F102" s="3">
         <v>-2004000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>5460000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>1246000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>165000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-41000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-604000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>143000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-2055000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-2325000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>2134000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>502000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-1094000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>231000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>2439000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>972000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-1214000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-1944000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>1058000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>1587000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-34000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>1934000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-1239000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-350000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>2763000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>1389000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-407000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>134000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>235000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>801000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>156000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>-4051000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>1111000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AL102" s="3">
         <v>-4128000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AM102" s="3">
         <v>5955000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AN102" s="3">
         <v>995000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AO102" s="3">
         <v>718000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AP102" s="3">
         <v>439000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AQ102" s="3">
         <v>1136000</v>
       </c>
     </row>
